--- a/Attainment Calculation/23 24 DCN 22414 Barate Batch SDP/CR3_22414 - Data Communication and Computer Network (1).xlsx
+++ b/Attainment Calculation/23 24 DCN 22414 Barate Batch SDP/CR3_22414 - Data Communication and Computer Network (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSBTE-28\Documents\ada\gpd_nba\Attainment Calculation\23 24 DCN 22414 Barate Batch SDP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDD7FDF-A891-48A0-915A-28759B59D775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C7DF2F-2369-44DE-8C9B-01C22788FB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO Set Target attain level" sheetId="1" r:id="rId1"/>
@@ -1052,7 +1052,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="50" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1332,6 +1332,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="16">
@@ -2562,7 +2574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3121,21 +3133,35 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3148,6 +3174,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3155,27 +3186,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3185,6 +3217,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3213,15 +3248,19 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3242,33 +3281,54 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="29" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3281,21 +3341,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="29" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3308,23 +3363,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3351,6 +3389,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3454,43 +3500,10 @@
     <xf numFmtId="2" fontId="3" fillId="4" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4210,10 +4223,10 @@
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="335" t="s">
+      <c r="D3" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="336"/>
+      <c r="E3" s="222"/>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -4222,10 +4235,10 @@
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="335">
+      <c r="D4" s="221">
         <v>22414</v>
       </c>
-      <c r="E4" s="336"/>
+      <c r="E4" s="222"/>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -4234,10 +4247,10 @@
       <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="335" t="s">
+      <c r="D5" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="336"/>
+      <c r="E5" s="222"/>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -4246,10 +4259,10 @@
       <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="335" t="s">
+      <c r="D6" s="347" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="336"/>
+      <c r="E6" s="348"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4268,7 +4281,7 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="339" t="s">
+      <c r="D8" s="201" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="8"/>
@@ -4280,7 +4293,7 @@
       <c r="C9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="339" t="s">
+      <c r="D9" s="201" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="8"/>
@@ -4292,7 +4305,7 @@
       <c r="C10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="339" t="s">
+      <c r="D10" s="201" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="8"/>
@@ -4304,7 +4317,7 @@
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="340" t="s">
+      <c r="D11" s="202" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="8"/>
@@ -4316,7 +4329,7 @@
       <c r="C12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="340" t="s">
+      <c r="D12" s="202" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="8"/>
@@ -4326,7 +4339,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="340"/>
+      <c r="D13" s="202"/>
       <c r="E13" s="8"/>
       <c r="F13" s="4"/>
     </row>
@@ -4371,31 +4384,31 @@
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B17" s="218" t="s">
+      <c r="B17" s="215" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="200" t="s">
+      <c r="C17" s="226" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="201"/>
-      <c r="E17" s="221" t="s">
+      <c r="D17" s="227"/>
+      <c r="E17" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="207"/>
-      <c r="G17" s="207"/>
-      <c r="H17" s="207"/>
-      <c r="I17" s="207"/>
-      <c r="J17" s="207"/>
-      <c r="K17" s="208"/>
-      <c r="L17" s="221" t="s">
+      <c r="F17" s="224"/>
+      <c r="G17" s="224"/>
+      <c r="H17" s="224"/>
+      <c r="I17" s="224"/>
+      <c r="J17" s="224"/>
+      <c r="K17" s="225"/>
+      <c r="L17" s="223" t="s">
         <v>24</v>
       </c>
-      <c r="M17" s="208"/>
+      <c r="M17" s="225"/>
     </row>
     <row r="18" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="219"/>
-      <c r="C18" s="202"/>
-      <c r="D18" s="203"/>
+      <c r="B18" s="216"/>
+      <c r="C18" s="228"/>
+      <c r="D18" s="229"/>
       <c r="E18" s="15" t="s">
         <v>25</v>
       </c>
@@ -4425,9 +4438,9 @@
       </c>
     </row>
     <row r="19" spans="1:25" ht="122.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="220"/>
-      <c r="C19" s="204"/>
-      <c r="D19" s="205"/>
+      <c r="B19" s="217"/>
+      <c r="C19" s="230"/>
+      <c r="D19" s="231"/>
       <c r="E19" s="16" t="s">
         <v>34</v>
       </c>
@@ -4468,31 +4481,31 @@
         <f t="shared" si="0"/>
         <v>Analyze the functioning of data communication and computer network.</v>
       </c>
-      <c r="E20" s="345">
+      <c r="E20" s="207">
         <v>3</v>
       </c>
-      <c r="F20" s="345">
+      <c r="F20" s="207">
         <v>2</v>
       </c>
-      <c r="G20" s="345" t="s">
+      <c r="G20" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="H20" s="345" t="s">
+      <c r="H20" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="I20" s="345" t="s">
+      <c r="I20" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="J20" s="346" t="s">
+      <c r="J20" s="208" t="s">
         <v>250</v>
       </c>
-      <c r="K20" s="345" t="s">
+      <c r="K20" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="L20" s="345">
+      <c r="L20" s="207">
         <v>2</v>
       </c>
-      <c r="M20" s="345">
+      <c r="M20" s="207">
         <v>1</v>
       </c>
     </row>
@@ -4508,31 +4521,31 @@
         <f t="shared" si="1"/>
         <v>Select relevant transmission media and switching techniques as per need.</v>
       </c>
-      <c r="E21" s="345">
+      <c r="E21" s="207">
         <v>2</v>
       </c>
-      <c r="F21" s="345">
+      <c r="F21" s="207">
         <v>2</v>
       </c>
-      <c r="G21" s="345">
+      <c r="G21" s="207">
         <v>2</v>
       </c>
-      <c r="H21" s="345" t="s">
+      <c r="H21" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="I21" s="345">
+      <c r="I21" s="207">
         <v>1</v>
       </c>
-      <c r="J21" s="346" t="s">
+      <c r="J21" s="208" t="s">
         <v>250</v>
       </c>
-      <c r="K21" s="345" t="s">
+      <c r="K21" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="L21" s="345">
+      <c r="L21" s="207">
         <v>2</v>
       </c>
-      <c r="M21" s="345">
+      <c r="M21" s="207">
         <v>2</v>
       </c>
     </row>
@@ -4548,31 +4561,31 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">Analyse the transmission errors with respect to IEEE standards. </v>
       </c>
-      <c r="E22" s="345">
+      <c r="E22" s="207">
         <v>3</v>
       </c>
-      <c r="F22" s="345">
+      <c r="F22" s="207">
         <v>2</v>
       </c>
-      <c r="G22" s="345" t="s">
+      <c r="G22" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="H22" s="345">
+      <c r="H22" s="207">
         <v>2</v>
       </c>
-      <c r="I22" s="345" t="s">
+      <c r="I22" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="J22" s="346" t="s">
+      <c r="J22" s="208" t="s">
         <v>250</v>
       </c>
-      <c r="K22" s="345" t="s">
+      <c r="K22" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="L22" s="345">
+      <c r="L22" s="207">
         <v>1</v>
       </c>
-      <c r="M22" s="345">
+      <c r="M22" s="207">
         <v>2</v>
       </c>
     </row>
@@ -4588,31 +4601,31 @@
         <f t="shared" si="3"/>
         <v>Configure various networking devices.</v>
       </c>
-      <c r="E23" s="345">
+      <c r="E23" s="207">
         <v>2</v>
       </c>
-      <c r="F23" s="345">
+      <c r="F23" s="207">
         <v>1</v>
       </c>
-      <c r="G23" s="345">
+      <c r="G23" s="207">
         <v>2</v>
       </c>
-      <c r="H23" s="345">
+      <c r="H23" s="207">
         <v>2</v>
       </c>
-      <c r="I23" s="345">
+      <c r="I23" s="207">
         <v>3</v>
       </c>
-      <c r="J23" s="346" t="s">
+      <c r="J23" s="208" t="s">
         <v>250</v>
       </c>
-      <c r="K23" s="345" t="s">
+      <c r="K23" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="L23" s="345">
+      <c r="L23" s="207">
         <v>3</v>
       </c>
-      <c r="M23" s="345">
+      <c r="M23" s="207">
         <v>3</v>
       </c>
     </row>
@@ -4628,31 +4641,31 @@
         <f t="shared" si="4"/>
         <v>Configure different TCP/IP services.</v>
       </c>
-      <c r="E24" s="345">
+      <c r="E24" s="207">
         <v>2</v>
       </c>
-      <c r="F24" s="345">
+      <c r="F24" s="207">
         <v>1</v>
       </c>
-      <c r="G24" s="345">
+      <c r="G24" s="207">
         <v>2</v>
       </c>
-      <c r="H24" s="345">
+      <c r="H24" s="207">
         <v>1</v>
       </c>
-      <c r="I24" s="345">
+      <c r="I24" s="207">
         <v>3</v>
       </c>
-      <c r="J24" s="346">
+      <c r="J24" s="208">
         <v>1</v>
       </c>
-      <c r="K24" s="345" t="s">
+      <c r="K24" s="207" t="s">
         <v>250</v>
       </c>
-      <c r="L24" s="345">
+      <c r="L24" s="207">
         <v>3</v>
       </c>
-      <c r="M24" s="345">
+      <c r="M24" s="207">
         <v>2</v>
       </c>
     </row>
@@ -4673,12 +4686,12 @@
       <c r="L25" s="20"/>
       <c r="M25" s="20"/>
     </row>
-    <row r="26" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="206" t="s">
+    <row r="26" spans="1:25" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="232" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="207"/>
-      <c r="D26" s="208"/>
+      <c r="C26" s="224"/>
+      <c r="D26" s="225"/>
       <c r="E26" s="18">
         <f t="shared" ref="E26:M26" si="5">IFERROR(AVERAGE(E20:E24),2)</f>
         <v>2.4</v>
@@ -4717,11 +4730,11 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="209" t="s">
+      <c r="B27" s="233" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="207"/>
-      <c r="D27" s="208"/>
+      <c r="C27" s="224"/>
+      <c r="D27" s="225"/>
       <c r="E27" s="26">
         <f t="shared" ref="E27:M27" si="6">E26</f>
         <v>2.4</v>
@@ -4765,7 +4778,7 @@
       <c r="D30" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="I30" s="215" t="s">
+      <c r="I30" s="218" t="s">
         <v>46</v>
       </c>
       <c r="J30" s="213"/>
@@ -4776,21 +4789,21 @@
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29"/>
       <c r="B31" s="29"/>
-      <c r="C31" s="216" t="s">
+      <c r="C31" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="217"/>
-      <c r="E31" s="217"/>
+      <c r="D31" s="220"/>
+      <c r="E31" s="220"/>
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
       <c r="H31" s="29"/>
-      <c r="I31" s="216" t="s">
+      <c r="I31" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="J31" s="217"/>
-      <c r="K31" s="217"/>
-      <c r="L31" s="217"/>
-      <c r="M31" s="217"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="220"/>
+      <c r="L31" s="220"/>
+      <c r="M31" s="220"/>
       <c r="N31" s="29"/>
       <c r="O31" s="29"/>
       <c r="P31" s="29"/>
@@ -5793,22 +5806,22 @@
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="I31:M31"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="E17:K17"/>
-    <mergeCell ref="L17:M17"/>
     <mergeCell ref="C17:D19"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="B17:B19"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="I31:M31"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="69" orientation="landscape"/>
@@ -5821,7 +5834,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B2:P17"/>
+  <dimension ref="B2:P28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
@@ -5835,262 +5848,378 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="343" t="s">
+      <c r="B2" s="205" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="341" t="s">
+      <c r="C2" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="341" t="s">
+      <c r="D2" s="203" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="341" t="s">
+      <c r="E2" s="203" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="341" t="s">
+      <c r="F2" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="341" t="s">
+      <c r="G2" s="203" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="341" t="s">
+      <c r="H2" s="203" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="341" t="s">
+      <c r="I2" s="203" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="341" t="s">
+      <c r="J2" s="203" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="341" t="s">
+      <c r="K2" s="203" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B3" s="341" t="s">
+      <c r="B3" s="203" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="342">
+      <c r="C3" s="204">
         <v>3</v>
       </c>
-      <c r="D3" s="342">
+      <c r="D3" s="204">
         <v>2</v>
       </c>
-      <c r="E3" s="342" t="s">
+      <c r="E3" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="F3" s="342" t="s">
+      <c r="F3" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="G3" s="342" t="s">
+      <c r="G3" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="H3" s="342" t="s">
+      <c r="H3" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="I3" s="342" t="s">
+      <c r="I3" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="J3" s="342">
+      <c r="J3" s="204">
         <v>2</v>
       </c>
-      <c r="K3" s="342">
+      <c r="K3" s="204">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="341" t="s">
+      <c r="B4" s="203" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="342">
+      <c r="C4" s="204">
         <v>2</v>
       </c>
-      <c r="D4" s="342">
+      <c r="D4" s="204">
         <v>2</v>
       </c>
-      <c r="E4" s="342">
+      <c r="E4" s="204">
         <v>2</v>
       </c>
-      <c r="F4" s="342" t="s">
+      <c r="F4" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="G4" s="342">
+      <c r="G4" s="204">
         <v>1</v>
       </c>
-      <c r="H4" s="342" t="s">
+      <c r="H4" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="I4" s="342" t="s">
+      <c r="I4" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="J4" s="342">
+      <c r="J4" s="204">
         <v>2</v>
       </c>
-      <c r="K4" s="342">
+      <c r="K4" s="204">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="341" t="s">
+      <c r="B5" s="203" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="342">
+      <c r="C5" s="204">
         <v>3</v>
       </c>
-      <c r="D5" s="342">
+      <c r="D5" s="204">
         <v>2</v>
       </c>
-      <c r="E5" s="342" t="s">
+      <c r="E5" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="F5" s="342">
+      <c r="F5" s="204">
         <v>2</v>
       </c>
-      <c r="G5" s="342" t="s">
+      <c r="G5" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="H5" s="342" t="s">
+      <c r="H5" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="I5" s="342" t="s">
+      <c r="I5" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="J5" s="342">
+      <c r="J5" s="204">
         <v>1</v>
       </c>
-      <c r="K5" s="342">
+      <c r="K5" s="204">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="341" t="s">
+      <c r="B6" s="203" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="342">
+      <c r="C6" s="204">
         <v>2</v>
       </c>
-      <c r="D6" s="342">
+      <c r="D6" s="204">
         <v>1</v>
       </c>
-      <c r="E6" s="342">
+      <c r="E6" s="204">
         <v>2</v>
       </c>
-      <c r="F6" s="342">
+      <c r="F6" s="204">
         <v>2</v>
       </c>
-      <c r="G6" s="342">
+      <c r="G6" s="204">
         <v>3</v>
       </c>
-      <c r="H6" s="342" t="s">
+      <c r="H6" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="I6" s="342" t="s">
+      <c r="I6" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="J6" s="342">
+      <c r="J6" s="204">
         <v>3</v>
       </c>
-      <c r="K6" s="342">
+      <c r="K6" s="204">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="341" t="s">
+      <c r="B7" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="342">
+      <c r="C7" s="204">
         <v>2</v>
       </c>
-      <c r="D7" s="342">
+      <c r="D7" s="204">
         <v>1</v>
       </c>
-      <c r="E7" s="342">
+      <c r="E7" s="204">
         <v>2</v>
       </c>
-      <c r="F7" s="342">
+      <c r="F7" s="204">
         <v>1</v>
       </c>
-      <c r="G7" s="342">
+      <c r="G7" s="204">
         <v>3</v>
       </c>
-      <c r="H7" s="342">
+      <c r="H7" s="204">
         <v>1</v>
       </c>
-      <c r="I7" s="342" t="s">
+      <c r="I7" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="J7" s="342">
+      <c r="J7" s="204">
         <v>3</v>
       </c>
-      <c r="K7" s="342">
+      <c r="K7" s="204">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="N9" s="343" t="s">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N9" s="205" t="s">
         <v>251</v>
       </c>
-      <c r="O9" s="343" t="s">
+      <c r="O9" s="205" t="s">
         <v>252</v>
       </c>
-      <c r="P9" s="343" t="s">
+      <c r="P9" s="205" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N10" s="343" t="s">
+      <c r="N10" s="205" t="s">
         <v>254</v>
       </c>
-      <c r="O10" s="344">
+      <c r="O10" s="206">
         <v>3</v>
       </c>
-      <c r="P10" s="344" t="s">
+      <c r="P10" s="206" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N11" s="343" t="s">
+      <c r="N11" s="205" t="s">
         <v>256</v>
       </c>
-      <c r="O11" s="344">
+      <c r="O11" s="206">
         <v>2</v>
       </c>
-      <c r="P11" s="344" t="s">
+      <c r="P11" s="206" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N12" s="343" t="s">
+      <c r="N12" s="205" t="s">
         <v>258</v>
       </c>
-      <c r="O12" s="344">
+      <c r="O12" s="206">
         <v>3</v>
       </c>
-      <c r="P12" s="344" t="s">
+      <c r="P12" s="206" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="16" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="347">
+      <c r="G16" s="209">
         <v>22414</v>
       </c>
-      <c r="H16" s="347">
+      <c r="H16" s="209">
         <v>100</v>
       </c>
-      <c r="I16" s="347">
+      <c r="I16" s="209">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="7:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="347" t="s">
+    <row r="17" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="209" t="s">
         <v>260</v>
       </c>
-      <c r="H17" s="347">
+      <c r="H17" s="209">
         <v>54.64</v>
       </c>
-      <c r="I17" s="347">
+      <c r="I17" s="209">
         <f>ROUNDUP((H17*70)/100,2)</f>
         <v>38.25</v>
+      </c>
+    </row>
+    <row r="23" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D23" s="200">
+        <v>1</v>
+      </c>
+      <c r="E23" s="200" t="s">
+        <v>244</v>
+      </c>
+      <c r="F23" s="200">
+        <v>2</v>
+      </c>
+      <c r="G23" s="200">
+        <v>2</v>
+      </c>
+      <c r="H23" s="200">
+        <v>2</v>
+      </c>
+      <c r="I23" s="200">
+        <v>4</v>
+      </c>
+      <c r="J23" s="200">
+        <v>4</v>
+      </c>
+      <c r="K23" s="200">
+        <v>4</v>
+      </c>
+      <c r="L23" s="200">
+        <f>SUM(F23:K23)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D24" s="200">
+        <v>2</v>
+      </c>
+      <c r="E24" s="200" t="s">
+        <v>245</v>
+      </c>
+      <c r="F24" s="200">
+        <v>2</v>
+      </c>
+      <c r="G24" s="200">
+        <v>2</v>
+      </c>
+      <c r="H24" s="200">
+        <v>2</v>
+      </c>
+      <c r="I24" s="200">
+        <v>4</v>
+      </c>
+      <c r="J24" s="200"/>
+      <c r="K24" s="200"/>
+      <c r="L24" s="200">
+        <f>SUM(F24:K24)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D25" s="200">
+        <v>3</v>
+      </c>
+      <c r="E25" s="200" t="s">
+        <v>246</v>
+      </c>
+      <c r="F25" s="200"/>
+      <c r="G25" s="200"/>
+      <c r="H25" s="200"/>
+      <c r="I25" s="200"/>
+      <c r="J25" s="200"/>
+      <c r="K25" s="200"/>
+      <c r="L25" s="200">
+        <f>SUM(F25:K25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D26" s="200">
+        <v>4</v>
+      </c>
+      <c r="E26" s="200" t="s">
+        <v>247</v>
+      </c>
+      <c r="F26" s="200"/>
+      <c r="G26" s="200"/>
+      <c r="H26" s="200"/>
+      <c r="I26" s="200"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="200"/>
+      <c r="L26" s="200">
+        <f>SUM(F26:K26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D27" s="200">
+        <v>5</v>
+      </c>
+      <c r="E27" s="200" t="s">
+        <v>248</v>
+      </c>
+      <c r="F27" s="200"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="200"/>
+      <c r="I27" s="200"/>
+      <c r="J27" s="200"/>
+      <c r="K27" s="200"/>
+      <c r="L27" s="200">
+        <f>SUM(F27:K27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="L28" s="200">
+        <f>SUM(L23:L27)</f>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -6103,7 +6232,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:AC999"/>
+  <dimension ref="A1:AC998"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6122,8 +6251,8 @@
     <col min="24" max="24" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="21.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="246" t="s">
+    <row r="1" spans="1:15" ht="21.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="257" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="213"/>
@@ -6141,8 +6270,8 @@
       <c r="N1" s="30"/>
       <c r="O1" s="30"/>
     </row>
-    <row r="2" spans="1:24" ht="21.75" x14ac:dyDescent="0.35">
-      <c r="A2" s="246" t="s">
+    <row r="2" spans="1:15" ht="21.75" x14ac:dyDescent="0.35">
+      <c r="A2" s="257" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="213"/>
@@ -6160,16 +6289,16 @@
       <c r="N2" s="30"/>
       <c r="O2" s="30"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="30"/>
       <c r="B3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="247" t="str">
+      <c r="C3" s="258" t="str">
         <f>'PO Set Target attain level'!D3</f>
         <v xml:space="preserve"> Data Communication and Computer Network</v>
       </c>
-      <c r="D3" s="248"/>
+      <c r="D3" s="259"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
@@ -6182,16 +6311,16 @@
       <c r="N3" s="30"/>
       <c r="O3" s="30"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="30"/>
       <c r="B4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="247">
+      <c r="C4" s="258">
         <f>'PO Set Target attain level'!D4</f>
         <v>22414</v>
       </c>
-      <c r="D4" s="248"/>
+      <c r="D4" s="259"/>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
@@ -6204,16 +6333,16 @@
       <c r="N4" s="30"/>
       <c r="O4" s="30"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="30"/>
       <c r="B5" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="247" t="str">
+      <c r="C5" s="258" t="str">
         <f>'PO Set Target attain level'!D5</f>
         <v>4th SEM(CO4I SCHEME)</v>
       </c>
-      <c r="D5" s="248"/>
+      <c r="D5" s="259"/>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -6225,45 +6354,17 @@
       <c r="M5" s="30"/>
       <c r="N5" s="30"/>
       <c r="O5" s="30"/>
-      <c r="P5" s="337">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="337" t="s">
-        <v>244</v>
-      </c>
-      <c r="R5" s="337">
-        <v>2</v>
-      </c>
-      <c r="S5" s="337">
-        <v>2</v>
-      </c>
-      <c r="T5" s="337">
-        <v>2</v>
-      </c>
-      <c r="U5" s="337">
-        <v>4</v>
-      </c>
-      <c r="V5" s="337">
-        <v>4</v>
-      </c>
-      <c r="W5" s="337">
-        <v>4</v>
-      </c>
-      <c r="X5" s="337">
-        <f>SUM(R5:W5)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="30"/>
       <c r="B6" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="247" t="str">
+      <c r="C6" s="258" t="str">
         <f>'PO Set Target attain level'!D6</f>
         <v>2023-24</v>
       </c>
-      <c r="D6" s="248"/>
+      <c r="D6" s="259"/>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
@@ -6275,32 +6376,8 @@
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
       <c r="O6" s="30"/>
-      <c r="P6" s="337">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="337" t="s">
-        <v>245</v>
-      </c>
-      <c r="R6" s="337">
-        <v>2</v>
-      </c>
-      <c r="S6" s="337">
-        <v>2</v>
-      </c>
-      <c r="T6" s="337">
-        <v>2</v>
-      </c>
-      <c r="U6" s="337">
-        <v>4</v>
-      </c>
-      <c r="V6" s="337"/>
-      <c r="W6" s="337"/>
-      <c r="X6" s="337">
-        <f t="shared" ref="X6:X9" si="0">SUM(R6:W6)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="30"/>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -6316,49 +6393,33 @@
       <c r="M7" s="30"/>
       <c r="N7" s="30"/>
       <c r="O7" s="30"/>
-      <c r="P7" s="337">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="337" t="s">
-        <v>246</v>
-      </c>
-      <c r="R7" s="337"/>
-      <c r="S7" s="337"/>
-      <c r="T7" s="337"/>
-      <c r="U7" s="337"/>
-      <c r="V7" s="337"/>
-      <c r="W7" s="337"/>
-      <c r="X7" s="337">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="249" t="s">
+    </row>
+    <row r="8" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="260" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="226" t="s">
+      <c r="B8" s="268" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="227" t="s">
+      <c r="C8" s="269" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="242" t="s">
+      <c r="D8" s="270" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="243" t="s">
+      <c r="E8" s="271" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="222" t="s">
+      <c r="F8" s="266" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="225" t="s">
+      <c r="G8" s="267" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="244" t="s">
+      <c r="H8" s="253" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="245" t="s">
+      <c r="I8" s="256" t="s">
         <v>62</v>
       </c>
       <c r="J8" s="32" t="s">
@@ -6371,100 +6432,64 @@
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
       <c r="O8" s="30"/>
-      <c r="P8" s="337">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="337" t="s">
-        <v>247</v>
-      </c>
-      <c r="R8" s="337"/>
-      <c r="S8" s="337"/>
-      <c r="T8" s="337"/>
-      <c r="U8" s="337"/>
-      <c r="V8" s="337"/>
-      <c r="W8" s="337"/>
-      <c r="X8" s="337">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="223"/>
-      <c r="B9" s="223"/>
-      <c r="C9" s="223"/>
-      <c r="D9" s="223"/>
-      <c r="E9" s="223"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="223"/>
-      <c r="H9" s="223"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="250" t="s">
+    </row>
+    <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="254"/>
+      <c r="B9" s="254"/>
+      <c r="C9" s="254"/>
+      <c r="D9" s="254"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="261" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="251"/>
+      <c r="K9" s="262"/>
       <c r="L9" s="30"/>
       <c r="M9" s="30"/>
       <c r="N9" s="30"/>
       <c r="O9" s="30"/>
-      <c r="P9" s="337">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="337" t="s">
-        <v>248</v>
-      </c>
-      <c r="R9" s="337"/>
-      <c r="S9" s="337"/>
-      <c r="T9" s="337"/>
-      <c r="U9" s="337"/>
-      <c r="V9" s="337"/>
-      <c r="W9" s="337"/>
-      <c r="X9" s="337">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="223"/>
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="223"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="252"/>
+    </row>
+    <row r="10" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="254"/>
+      <c r="B10" s="254"/>
+      <c r="C10" s="254"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="254"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="254"/>
+      <c r="I10" s="254"/>
+      <c r="J10" s="263"/>
       <c r="K10" s="211"/>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
       <c r="O10" s="30"/>
-      <c r="X10" s="338">
-        <f>SUM(X5:X9)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="223"/>
-      <c r="B11" s="223"/>
-      <c r="C11" s="223"/>
-      <c r="D11" s="224"/>
-      <c r="E11" s="224"/>
-      <c r="F11" s="224"/>
-      <c r="G11" s="224"/>
-      <c r="H11" s="224"/>
-      <c r="I11" s="224"/>
-      <c r="J11" s="253"/>
-      <c r="K11" s="254"/>
+    </row>
+    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="254"/>
+      <c r="B11" s="254"/>
+      <c r="C11" s="254"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="265"/>
       <c r="L11" s="30"/>
       <c r="M11" s="30"/>
       <c r="N11" s="30"/>
       <c r="O11" s="30"/>
     </row>
-    <row r="12" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="224"/>
-      <c r="B12" s="224"/>
-      <c r="C12" s="224"/>
+    <row r="12" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="255"/>
+      <c r="B12" s="255"/>
+      <c r="C12" s="255"/>
       <c r="D12" s="33">
         <v>18</v>
       </c>
@@ -6482,18 +6507,18 @@
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="37">
-        <f t="shared" ref="J12:J69" si="1">D12+E12</f>
+        <f t="shared" ref="J12:J69" si="0">D12+E12</f>
         <v>32</v>
       </c>
       <c r="K12" s="37">
-        <f t="shared" ref="K12:K69" si="2">G12+H12+I12+F12</f>
+        <f t="shared" ref="K12:K69" si="1">G12+H12+I12+F12</f>
         <v>32</v>
       </c>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
       <c r="N12" s="38"/>
     </row>
-    <row r="13" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>1</v>
       </c>
@@ -6520,18 +6545,18 @@
       </c>
       <c r="I13" s="39"/>
       <c r="J13" s="37">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K13" s="43">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K13" s="43">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="L13" s="30"/>
       <c r="M13" s="30"/>
       <c r="N13" s="38"/>
     </row>
-    <row r="14" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2</v>
       </c>
@@ -6558,18 +6583,18 @@
       </c>
       <c r="I14" s="39"/>
       <c r="J14" s="37">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="K14" s="43">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="K14" s="43">
-        <f t="shared" si="2"/>
         <v>12.5</v>
       </c>
       <c r="L14" s="30"/>
       <c r="M14" s="30"/>
       <c r="N14" s="38"/>
     </row>
-    <row r="15" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>3</v>
       </c>
@@ -6596,18 +6621,18 @@
       </c>
       <c r="I15" s="39"/>
       <c r="J15" s="37">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="K15" s="43">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="K15" s="43">
-        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="L15" s="30"/>
       <c r="M15" s="30"/>
       <c r="N15" s="38"/>
     </row>
-    <row r="16" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>4</v>
       </c>
@@ -6634,11 +6659,11 @@
       </c>
       <c r="I16" s="39"/>
       <c r="J16" s="37">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="K16" s="43">
         <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="K16" s="43">
-        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="L16" s="30"/>
@@ -6672,11 +6697,11 @@
       </c>
       <c r="I17" s="39"/>
       <c r="J17" s="37">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="K17" s="43">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K17" s="43">
-        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="L17" s="30"/>
@@ -6710,11 +6735,11 @@
       </c>
       <c r="I18" s="39"/>
       <c r="J18" s="37">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="K18" s="43">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K18" s="43">
-        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L18" s="30"/>
@@ -6748,11 +6773,11 @@
       </c>
       <c r="I19" s="39"/>
       <c r="J19" s="37">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="K19" s="43">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="K19" s="43">
-        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L19" s="30"/>
@@ -6798,11 +6823,11 @@
       </c>
       <c r="I20" s="39"/>
       <c r="J20" s="37">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="K20" s="43">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="K20" s="43">
-        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="L20" s="30"/>
@@ -6848,11 +6873,11 @@
       </c>
       <c r="I21" s="39"/>
       <c r="J21" s="37">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="K21" s="43">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="K21" s="43">
-        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="L21" s="30"/>
@@ -6898,11 +6923,11 @@
       </c>
       <c r="I22" s="39"/>
       <c r="J22" s="37">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="K22" s="43">
         <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="K22" s="43">
-        <f t="shared" si="2"/>
         <v>12.5</v>
       </c>
       <c r="L22" s="30"/>
@@ -6948,11 +6973,11 @@
       </c>
       <c r="I23" s="39"/>
       <c r="J23" s="37">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="K23" s="43">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="K23" s="43">
-        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="L23" s="30"/>
@@ -6998,11 +7023,11 @@
       </c>
       <c r="I24" s="39"/>
       <c r="J24" s="37">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="K24" s="43">
         <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="K24" s="43">
-        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="L24" s="30"/>
@@ -7048,11 +7073,11 @@
       </c>
       <c r="I25" s="39"/>
       <c r="J25" s="37">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="K25" s="43">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K25" s="43">
-        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L25" s="30"/>
@@ -7098,11 +7123,11 @@
       </c>
       <c r="I26" s="39"/>
       <c r="J26" s="37">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="K26" s="43">
         <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="K26" s="43">
-        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L26" s="30"/>
@@ -7148,11 +7173,11 @@
       </c>
       <c r="I27" s="39"/>
       <c r="J27" s="37">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="K27" s="43">
         <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="K27" s="43">
-        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L27" s="30"/>
@@ -7186,11 +7211,11 @@
       </c>
       <c r="I28" s="39"/>
       <c r="J28" s="37">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="K28" s="43">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="K28" s="43">
-        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="L28" s="30"/>
@@ -7224,11 +7249,11 @@
       </c>
       <c r="I29" s="39"/>
       <c r="J29" s="37">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="K29" s="43">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="K29" s="43">
-        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="L29" s="30"/>
@@ -7262,11 +7287,11 @@
       </c>
       <c r="I30" s="39"/>
       <c r="J30" s="37">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="K30" s="43">
         <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="K30" s="43">
-        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="L30" s="30"/>
@@ -7300,11 +7325,11 @@
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="37">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="K31" s="43">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="K31" s="43">
-        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="L31" s="30"/>
@@ -7338,11 +7363,11 @@
       </c>
       <c r="I32" s="39"/>
       <c r="J32" s="37">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="K32" s="43">
         <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="K32" s="43">
-        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="L32" s="30"/>
@@ -7376,11 +7401,11 @@
       </c>
       <c r="I33" s="39"/>
       <c r="J33" s="37">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="K33" s="43">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="K33" s="43">
-        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L33" s="30"/>
@@ -7414,11 +7439,11 @@
       </c>
       <c r="I34" s="39"/>
       <c r="J34" s="37">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="K34" s="43">
         <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="K34" s="43">
-        <f t="shared" si="2"/>
         <v>5.5</v>
       </c>
       <c r="L34" s="30"/>
@@ -7452,11 +7477,11 @@
       </c>
       <c r="I35" s="39"/>
       <c r="J35" s="37">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="K35" s="43">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="K35" s="43">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L35" s="30"/>
@@ -7490,11 +7515,11 @@
       </c>
       <c r="I36" s="39"/>
       <c r="J36" s="37">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="K36" s="43">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="K36" s="43">
-        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="L36" s="30"/>
@@ -7528,11 +7553,11 @@
       </c>
       <c r="I37" s="39"/>
       <c r="J37" s="37">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="K37" s="43">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="K37" s="43">
-        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="L37" s="30"/>
@@ -7566,11 +7591,11 @@
       </c>
       <c r="I38" s="39"/>
       <c r="J38" s="37">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K38" s="43">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="K38" s="43">
-        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="L38" s="30"/>
@@ -7604,11 +7629,11 @@
       </c>
       <c r="I39" s="39"/>
       <c r="J39" s="37">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="K39" s="43">
         <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="K39" s="43">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="L39" s="30"/>
@@ -7642,11 +7667,11 @@
       </c>
       <c r="I40" s="39"/>
       <c r="J40" s="37">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K40" s="43">
         <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="K40" s="43">
-        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L40" s="30"/>
@@ -7680,11 +7705,11 @@
       </c>
       <c r="I41" s="39"/>
       <c r="J41" s="37">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="K41" s="43">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="K41" s="43">
-        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="L41" s="30"/>
@@ -7718,11 +7743,11 @@
       </c>
       <c r="I42" s="39"/>
       <c r="J42" s="37">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="K42" s="43">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K42" s="43">
-        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="L42" s="30"/>
@@ -7756,11 +7781,11 @@
       </c>
       <c r="I43" s="39"/>
       <c r="J43" s="37">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="K43" s="43">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="K43" s="43">
-        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="L43" s="30"/>
@@ -7794,11 +7819,11 @@
       </c>
       <c r="I44" s="39"/>
       <c r="J44" s="37">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="K44" s="43">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="K44" s="43">
-        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="L44" s="30"/>
@@ -7832,11 +7857,11 @@
       </c>
       <c r="I45" s="39"/>
       <c r="J45" s="37">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K45" s="43">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="K45" s="43">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L45" s="30"/>
@@ -7870,11 +7895,11 @@
       </c>
       <c r="I46" s="39"/>
       <c r="J46" s="37">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="K46" s="43">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="K46" s="43">
-        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="L46" s="30"/>
@@ -7908,11 +7933,11 @@
       </c>
       <c r="I47" s="39"/>
       <c r="J47" s="37">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K47" s="43">
         <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="K47" s="43">
-        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="L47" s="30"/>
@@ -7946,11 +7971,11 @@
       </c>
       <c r="I48" s="39"/>
       <c r="J48" s="37">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="K48" s="43">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="K48" s="43">
-        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="L48" s="30"/>
@@ -7984,11 +8009,11 @@
       </c>
       <c r="I49" s="39"/>
       <c r="J49" s="37">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="K49" s="43">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="K49" s="43">
-        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="L49" s="30"/>
@@ -8022,11 +8047,11 @@
       </c>
       <c r="I50" s="39"/>
       <c r="J50" s="37">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="K50" s="43">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="K50" s="43">
-        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="L50" s="30"/>
@@ -8060,11 +8085,11 @@
       </c>
       <c r="I51" s="39"/>
       <c r="J51" s="37">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K51" s="43">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="K51" s="43">
-        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="L51" s="30"/>
@@ -8098,11 +8123,11 @@
       </c>
       <c r="I52" s="39"/>
       <c r="J52" s="37">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="K52" s="43">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="K52" s="43">
-        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="L52" s="30"/>
@@ -8136,11 +8161,11 @@
       </c>
       <c r="I53" s="39"/>
       <c r="J53" s="37">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="K53" s="43">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="K53" s="43">
-        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="L53" s="30"/>
@@ -8174,11 +8199,11 @@
       </c>
       <c r="I54" s="39"/>
       <c r="J54" s="37">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="K54" s="43">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="K54" s="43">
-        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="L54" s="30"/>
@@ -8212,11 +8237,11 @@
       </c>
       <c r="I55" s="39"/>
       <c r="J55" s="37">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="K55" s="43">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="K55" s="43">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="L55" s="30"/>
@@ -8250,11 +8275,11 @@
       </c>
       <c r="I56" s="39"/>
       <c r="J56" s="37">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="K56" s="43">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="K56" s="43">
-        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="L56" s="30"/>
@@ -8288,11 +8313,11 @@
       </c>
       <c r="I57" s="39"/>
       <c r="J57" s="37">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="K57" s="43">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K57" s="43">
-        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="L57" s="30"/>
@@ -8326,11 +8351,11 @@
       </c>
       <c r="I58" s="39"/>
       <c r="J58" s="37">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="K58" s="43">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="K58" s="43">
-        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="L58" s="30"/>
@@ -8364,11 +8389,11 @@
       </c>
       <c r="I59" s="39"/>
       <c r="J59" s="37">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="K59" s="43">
         <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="K59" s="43">
-        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="L59" s="30"/>
@@ -8402,11 +8427,11 @@
       </c>
       <c r="I60" s="39"/>
       <c r="J60" s="37">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="K60" s="43">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="K60" s="43">
-        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L60" s="30"/>
@@ -8440,11 +8465,11 @@
       </c>
       <c r="I61" s="39"/>
       <c r="J61" s="37">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="K61" s="43">
         <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="K61" s="43">
-        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="L61" s="30"/>
@@ -8478,11 +8503,11 @@
       </c>
       <c r="I62" s="39"/>
       <c r="J62" s="37">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="K62" s="43">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="K62" s="43">
-        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="L62" s="30"/>
@@ -8516,11 +8541,11 @@
       </c>
       <c r="I63" s="39"/>
       <c r="J63" s="37">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="K63" s="43">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="K63" s="43">
-        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="L63" s="30"/>
@@ -8554,11 +8579,11 @@
       </c>
       <c r="I64" s="39"/>
       <c r="J64" s="37">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K64" s="43">
         <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="K64" s="43">
-        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="L64" s="30"/>
@@ -8592,11 +8617,11 @@
       </c>
       <c r="I65" s="39"/>
       <c r="J65" s="37">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K65" s="37">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="K65" s="37">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="L65" s="30"/>
@@ -8630,11 +8655,11 @@
       </c>
       <c r="I66" s="39"/>
       <c r="J66" s="37">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="K66" s="37">
         <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="K66" s="37">
-        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="L66" s="30"/>
@@ -8668,11 +8693,11 @@
       </c>
       <c r="I67" s="39"/>
       <c r="J67" s="37">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="K67" s="37">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="K67" s="37">
-        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="L67" s="30"/>
@@ -8706,11 +8731,11 @@
       </c>
       <c r="I68" s="39"/>
       <c r="J68" s="37">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="K68" s="37">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="K68" s="37">
-        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="L68" s="30"/>
@@ -8745,11 +8770,11 @@
       </c>
       <c r="I69" s="39"/>
       <c r="J69" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K69" s="37">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L69" s="30"/>
@@ -8784,11 +8809,11 @@
       </c>
       <c r="I70" s="39"/>
       <c r="J70" s="37">
-        <f t="shared" ref="J70:J74" si="3">D70+E70</f>
+        <f t="shared" ref="J70:J74" si="2">D70+E70</f>
         <v>0</v>
       </c>
       <c r="K70" s="37">
-        <f t="shared" ref="K70:K74" si="4">G70+H70+I70+F70</f>
+        <f t="shared" ref="K70:K74" si="3">G70+H70+I70+F70</f>
         <v>0</v>
       </c>
       <c r="L70" s="30"/>
@@ -8823,11 +8848,11 @@
       </c>
       <c r="I71" s="39"/>
       <c r="J71" s="37">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="K71" s="37">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="K71" s="37">
-        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="L71" s="30"/>
@@ -8862,11 +8887,11 @@
       </c>
       <c r="I72" s="39"/>
       <c r="J72" s="37">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="K72" s="37">
         <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="K72" s="37">
-        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="L72" s="30"/>
@@ -8901,11 +8926,11 @@
       </c>
       <c r="I73" s="39"/>
       <c r="J73" s="37">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="K73" s="37">
         <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="K73" s="37">
-        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="L73" s="30"/>
@@ -8940,11 +8965,11 @@
       </c>
       <c r="I74" s="39"/>
       <c r="J74" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K74" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K74" s="37">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L74" s="30"/>
@@ -8965,11 +8990,11 @@
       <c r="H75" s="39"/>
       <c r="I75" s="39"/>
       <c r="J75" s="37">
-        <f t="shared" ref="J74:J94" si="5">D75+E75+F75</f>
+        <f t="shared" ref="J75:J94" si="4">D75+E75+F75</f>
         <v>0</v>
       </c>
       <c r="K75" s="37">
-        <f t="shared" ref="K74:K94" si="6">G75+H75+I75</f>
+        <f t="shared" ref="K75:K94" si="5">G75+H75+I75</f>
         <v>0</v>
       </c>
       <c r="L75" s="30"/>
@@ -8990,11 +9015,11 @@
       <c r="H76" s="39"/>
       <c r="I76" s="39"/>
       <c r="J76" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K76" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K76" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L76" s="30"/>
@@ -9015,11 +9040,11 @@
       <c r="H77" s="42"/>
       <c r="I77" s="39"/>
       <c r="J77" s="43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="43">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="43">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L77" s="30"/>
@@ -9040,11 +9065,11 @@
       <c r="H78" s="42"/>
       <c r="I78" s="39"/>
       <c r="J78" s="43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K78" s="43">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="43">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L78" s="30"/>
@@ -9065,11 +9090,11 @@
       <c r="H79" s="39"/>
       <c r="I79" s="39"/>
       <c r="J79" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K79" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K79" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L79" s="30"/>
@@ -9090,11 +9115,11 @@
       <c r="H80" s="39"/>
       <c r="I80" s="39"/>
       <c r="J80" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K80" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L80" s="30"/>
@@ -9115,11 +9140,11 @@
       <c r="H81" s="39"/>
       <c r="I81" s="39"/>
       <c r="J81" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K81" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K81" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L81" s="30"/>
@@ -9140,11 +9165,11 @@
       <c r="H82" s="39"/>
       <c r="I82" s="39"/>
       <c r="J82" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K82" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K82" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L82" s="30"/>
@@ -9165,11 +9190,11 @@
       <c r="H83" s="39"/>
       <c r="I83" s="39"/>
       <c r="J83" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K83" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L83" s="30"/>
@@ -9190,11 +9215,11 @@
       <c r="H84" s="39"/>
       <c r="I84" s="39"/>
       <c r="J84" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K84" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K84" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L84" s="30"/>
@@ -9215,11 +9240,11 @@
       <c r="H85" s="39"/>
       <c r="I85" s="39"/>
       <c r="J85" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K85" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L85" s="30"/>
@@ -9240,11 +9265,11 @@
       <c r="H86" s="39"/>
       <c r="I86" s="39"/>
       <c r="J86" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K86" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K86" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L86" s="30"/>
@@ -9265,11 +9290,11 @@
       <c r="H87" s="39"/>
       <c r="I87" s="39"/>
       <c r="J87" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K87" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K87" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L87" s="30"/>
@@ -9290,11 +9315,11 @@
       <c r="H88" s="39"/>
       <c r="I88" s="39"/>
       <c r="J88" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K88" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K88" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L88" s="30"/>
@@ -9315,11 +9340,11 @@
       <c r="H89" s="39"/>
       <c r="I89" s="39"/>
       <c r="J89" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K89" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K89" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L89" s="30"/>
@@ -9340,11 +9365,11 @@
       <c r="H90" s="39"/>
       <c r="I90" s="39"/>
       <c r="J90" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K90" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K90" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L90" s="30"/>
@@ -9365,11 +9390,11 @@
       <c r="H91" s="39"/>
       <c r="I91" s="39"/>
       <c r="J91" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K91" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K91" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L91" s="30"/>
@@ -9390,11 +9415,11 @@
       <c r="H92" s="39"/>
       <c r="I92" s="39"/>
       <c r="J92" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K92" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L92" s="30"/>
@@ -9415,11 +9440,11 @@
       <c r="H93" s="39"/>
       <c r="I93" s="39"/>
       <c r="J93" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K93" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K93" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L93" s="30"/>
@@ -9440,11 +9465,11 @@
       <c r="H94" s="39"/>
       <c r="I94" s="39"/>
       <c r="J94" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K94" s="37">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K94" s="37">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L94" s="30"/>
@@ -9453,58 +9478,58 @@
       <c r="O94" s="30"/>
     </row>
     <row r="95" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="228" t="s">
+      <c r="A95" s="234" t="s">
         <v>128</v>
       </c>
       <c r="B95" s="213"/>
       <c r="C95" s="57">
         <v>0.4</v>
       </c>
-      <c r="D95" s="229">
-        <f t="shared" ref="D95:I95" si="7">$C$95*D12</f>
+      <c r="D95" s="235">
+        <f t="shared" ref="D95:I95" si="6">$C$95*D12</f>
         <v>7.2</v>
       </c>
-      <c r="E95" s="229">
-        <f t="shared" si="7"/>
+      <c r="E95" s="235">
+        <f t="shared" si="6"/>
         <v>5.6000000000000005</v>
       </c>
-      <c r="F95" s="229">
-        <f t="shared" si="7"/>
+      <c r="F95" s="235">
+        <f t="shared" si="6"/>
         <v>3.2</v>
       </c>
-      <c r="G95" s="229">
-        <f t="shared" si="7"/>
+      <c r="G95" s="235">
+        <f t="shared" si="6"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="H95" s="229">
-        <f t="shared" si="7"/>
+      <c r="H95" s="235">
+        <f t="shared" si="6"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="I95" s="229">
-        <f t="shared" si="7"/>
+      <c r="I95" s="235">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J95" s="255"/>
-      <c r="K95" s="255"/>
+      <c r="J95" s="272"/>
+      <c r="K95" s="272"/>
       <c r="L95" s="30"/>
       <c r="M95" s="30"/>
       <c r="N95" s="30"/>
       <c r="O95" s="30"/>
     </row>
     <row r="96" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="230" t="s">
+      <c r="A96" s="236" t="s">
         <v>129</v>
       </c>
       <c r="B96" s="213"/>
-      <c r="C96" s="203"/>
-      <c r="D96" s="220"/>
-      <c r="E96" s="220"/>
-      <c r="F96" s="220"/>
-      <c r="G96" s="220"/>
-      <c r="H96" s="220"/>
-      <c r="I96" s="220"/>
-      <c r="J96" s="220"/>
-      <c r="K96" s="220"/>
+      <c r="C96" s="229"/>
+      <c r="D96" s="217"/>
+      <c r="E96" s="217"/>
+      <c r="F96" s="217"/>
+      <c r="G96" s="217"/>
+      <c r="H96" s="217"/>
+      <c r="I96" s="217"/>
+      <c r="J96" s="217"/>
+      <c r="K96" s="217"/>
       <c r="L96" s="30"/>
       <c r="M96" s="30"/>
       <c r="N96" s="30"/>
@@ -9513,33 +9538,33 @@
     <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="213"/>
       <c r="B97" s="213"/>
-      <c r="C97" s="203"/>
-      <c r="D97" s="257">
-        <f t="shared" ref="D97:I97" si="8">COUNTIF(D13:D94,"&gt;=" &amp;D95)</f>
+      <c r="C97" s="229"/>
+      <c r="D97" s="237">
+        <f t="shared" ref="D97:I97" si="7">COUNTIF(D13:D94,"&gt;=" &amp;D95)</f>
         <v>50</v>
       </c>
-      <c r="E97" s="257">
-        <f t="shared" si="8"/>
+      <c r="E97" s="237">
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="F97" s="257">
-        <f t="shared" si="8"/>
+      <c r="F97" s="237">
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
-      <c r="G97" s="257">
-        <f t="shared" si="8"/>
+      <c r="G97" s="237">
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="H97" s="257">
-        <f t="shared" si="8"/>
+      <c r="H97" s="237">
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="I97" s="257">
-        <f t="shared" si="8"/>
+      <c r="I97" s="237">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J97" s="256"/>
-      <c r="K97" s="256"/>
+      <c r="J97" s="273"/>
+      <c r="K97" s="273"/>
       <c r="L97" s="30"/>
       <c r="M97" s="30"/>
       <c r="N97" s="30"/>
@@ -9549,14 +9574,14 @@
       <c r="A98" s="30"/>
       <c r="B98" s="30"/>
       <c r="C98" s="30"/>
-      <c r="D98" s="220"/>
-      <c r="E98" s="220"/>
-      <c r="F98" s="220"/>
-      <c r="G98" s="220"/>
-      <c r="H98" s="220"/>
-      <c r="I98" s="220"/>
-      <c r="J98" s="220"/>
-      <c r="K98" s="220"/>
+      <c r="D98" s="217"/>
+      <c r="E98" s="217"/>
+      <c r="F98" s="217"/>
+      <c r="G98" s="217"/>
+      <c r="H98" s="217"/>
+      <c r="I98" s="217"/>
+      <c r="J98" s="217"/>
+      <c r="K98" s="217"/>
       <c r="L98" s="30"/>
       <c r="M98" s="30"/>
       <c r="N98" s="30"/>
@@ -9615,21 +9640,21 @@
     </row>
     <row r="102" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="30"/>
-      <c r="B102" s="235" t="s">
+      <c r="B102" s="242" t="s">
         <v>130</v>
       </c>
-      <c r="C102" s="207"/>
-      <c r="D102" s="207"/>
-      <c r="E102" s="208"/>
-      <c r="F102" s="236" t="s">
+      <c r="C102" s="224"/>
+      <c r="D102" s="224"/>
+      <c r="E102" s="225"/>
+      <c r="F102" s="243" t="s">
         <v>131</v>
       </c>
-      <c r="G102" s="208"/>
+      <c r="G102" s="225"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="237" t="s">
+      <c r="I102" s="244" t="s">
         <v>132</v>
       </c>
-      <c r="J102" s="208"/>
+      <c r="J102" s="225"/>
       <c r="K102" s="30"/>
       <c r="L102" s="30"/>
       <c r="M102" s="30"/>
@@ -9638,28 +9663,28 @@
     </row>
     <row r="103" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="30"/>
-      <c r="B103" s="238" t="s">
+      <c r="B103" s="245" t="s">
         <v>133</v>
       </c>
-      <c r="C103" s="231" t="s">
+      <c r="C103" s="238" t="s">
         <v>134</v>
       </c>
-      <c r="D103" s="207"/>
+      <c r="D103" s="224"/>
       <c r="E103" s="59">
         <v>50</v>
       </c>
-      <c r="F103" s="241">
+      <c r="F103" s="248">
         <v>62</v>
       </c>
-      <c r="G103" s="201"/>
+      <c r="G103" s="227"/>
       <c r="H103" s="60">
         <f>E103*F103/100</f>
         <v>31</v>
       </c>
-      <c r="I103" s="258">
+      <c r="I103" s="249">
         <v>1</v>
       </c>
-      <c r="J103" s="259"/>
+      <c r="J103" s="250"/>
       <c r="K103" s="30"/>
       <c r="L103" s="30"/>
       <c r="M103" s="30"/>
@@ -9668,24 +9693,24 @@
     </row>
     <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="30"/>
-      <c r="B104" s="239"/>
-      <c r="C104" s="231" t="s">
+      <c r="B104" s="246"/>
+      <c r="C104" s="238" t="s">
         <v>134</v>
       </c>
-      <c r="D104" s="207"/>
+      <c r="D104" s="224"/>
       <c r="E104" s="59">
         <v>60</v>
       </c>
-      <c r="F104" s="202"/>
-      <c r="G104" s="203"/>
+      <c r="F104" s="228"/>
+      <c r="G104" s="229"/>
       <c r="H104" s="61">
         <f>E104*F103/100</f>
         <v>37.200000000000003</v>
       </c>
-      <c r="I104" s="260">
+      <c r="I104" s="251">
         <v>2</v>
       </c>
-      <c r="J104" s="261"/>
+      <c r="J104" s="252"/>
       <c r="K104" s="30"/>
       <c r="L104" s="30"/>
       <c r="M104" s="30"/>
@@ -9694,24 +9719,24 @@
     </row>
     <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="30"/>
-      <c r="B105" s="240"/>
-      <c r="C105" s="231" t="s">
+      <c r="B105" s="247"/>
+      <c r="C105" s="238" t="s">
         <v>134</v>
       </c>
-      <c r="D105" s="207"/>
+      <c r="D105" s="224"/>
       <c r="E105" s="62">
         <v>70</v>
       </c>
-      <c r="F105" s="204"/>
-      <c r="G105" s="205"/>
+      <c r="F105" s="230"/>
+      <c r="G105" s="231"/>
       <c r="H105" s="63">
         <f>E105*F103/100</f>
         <v>43.4</v>
       </c>
-      <c r="I105" s="232">
+      <c r="I105" s="239">
         <v>3</v>
       </c>
-      <c r="J105" s="233"/>
+      <c r="J105" s="240"/>
       <c r="K105" s="30"/>
       <c r="L105" s="30"/>
       <c r="M105" s="30"/>
@@ -9726,9 +9751,9 @@
       <c r="E106" s="64"/>
       <c r="F106" s="64"/>
       <c r="G106" s="64"/>
-      <c r="H106" s="234"/>
-      <c r="I106" s="217"/>
-      <c r="J106" s="217"/>
+      <c r="H106" s="241"/>
+      <c r="I106" s="220"/>
+      <c r="J106" s="220"/>
       <c r="K106" s="30"/>
       <c r="L106" s="30"/>
       <c r="M106" s="30"/>
@@ -9743,9 +9768,9 @@
       <c r="E107" s="64"/>
       <c r="F107" s="64"/>
       <c r="G107" s="64"/>
-      <c r="H107" s="234"/>
-      <c r="I107" s="217"/>
-      <c r="J107" s="217"/>
+      <c r="H107" s="241"/>
+      <c r="I107" s="220"/>
+      <c r="J107" s="220"/>
       <c r="K107" s="30"/>
       <c r="L107" s="30"/>
       <c r="M107" s="30"/>
@@ -9790,27 +9815,27 @@
         <v>138</v>
       </c>
       <c r="D109" s="69">
-        <f t="shared" ref="D109:I109" si="9">IF(D97&gt;=$H105,3,IF(D97&gt;=$H104,2,IF(D97&gt;=$H103,1,0)))</f>
+        <f t="shared" ref="D109:I109" si="8">IF(D97&gt;=$H105,3,IF(D97&gt;=$H104,2,IF(D97&gt;=$H103,1,0)))</f>
         <v>3</v>
       </c>
       <c r="E109" s="69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="F109" s="69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G109" s="69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H109" s="69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="I109" s="69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J109" s="64"/>
@@ -9871,7 +9896,7 @@
       <c r="N112" s="30"/>
       <c r="O112" s="30"/>
     </row>
-    <row r="113" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="30"/>
       <c r="B113" s="30"/>
       <c r="C113" s="30"/>
@@ -9888,7 +9913,7 @@
       <c r="N113" s="30"/>
       <c r="O113" s="30"/>
     </row>
-    <row r="114" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="30"/>
       <c r="B114" s="30"/>
       <c r="C114" s="30"/>
@@ -9979,7 +10004,9 @@
       <c r="C119" s="30"/>
       <c r="D119" s="30"/>
       <c r="E119" s="30"/>
-      <c r="F119" s="30"/>
+      <c r="F119" s="30" t="s">
+        <v>139</v>
+      </c>
       <c r="G119" s="30"/>
       <c r="H119" s="30"/>
       <c r="I119" s="30"/>
@@ -9996,9 +10023,7 @@
       <c r="C120" s="30"/>
       <c r="D120" s="30"/>
       <c r="E120" s="30"/>
-      <c r="F120" s="30" t="s">
-        <v>139</v>
-      </c>
+      <c r="F120" s="30"/>
       <c r="G120" s="30"/>
       <c r="H120" s="30"/>
       <c r="I120" s="30"/>
@@ -13392,23 +13417,7 @@
       <c r="N319" s="30"/>
       <c r="O319" s="30"/>
     </row>
-    <row r="320" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A320" s="30"/>
-      <c r="B320" s="30"/>
-      <c r="C320" s="30"/>
-      <c r="D320" s="30"/>
-      <c r="E320" s="30"/>
-      <c r="F320" s="30"/>
-      <c r="G320" s="30"/>
-      <c r="H320" s="30"/>
-      <c r="I320" s="30"/>
-      <c r="J320" s="30"/>
-      <c r="K320" s="30"/>
-      <c r="L320" s="30"/>
-      <c r="M320" s="30"/>
-      <c r="N320" s="30"/>
-      <c r="O320" s="30"/>
-    </row>
+    <row r="320" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14087,7 +14096,6 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="47">
     <mergeCell ref="H95:H96"/>
@@ -14108,6 +14116,12 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="J9:K11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="E8:E11"/>
     <mergeCell ref="C105:D105"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="H106:J106"/>
@@ -14121,17 +14135,11 @@
     <mergeCell ref="C104:D104"/>
     <mergeCell ref="I103:J103"/>
     <mergeCell ref="I104:J104"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C8:C12"/>
     <mergeCell ref="A95:B95"/>
     <mergeCell ref="E95:E96"/>
     <mergeCell ref="F95:F96"/>
     <mergeCell ref="G95:G96"/>
     <mergeCell ref="A96:C97"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="E8:E11"/>
     <mergeCell ref="D95:D96"/>
     <mergeCell ref="D97:D98"/>
     <mergeCell ref="E97:E98"/>
@@ -14162,7 +14170,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B1" s="262" t="s">
+      <c r="B1" s="274" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="213"/>
@@ -14237,11 +14245,11 @@
       <c r="C4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="263" t="str">
+      <c r="D4" s="275" t="str">
         <f>'CO_Attainment for Unit Tests'!C3</f>
         <v xml:space="preserve"> Data Communication and Computer Network</v>
       </c>
-      <c r="E4" s="217"/>
+      <c r="E4" s="220"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
       <c r="H4" s="30"/>
@@ -14265,11 +14273,11 @@
       <c r="C5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="263">
+      <c r="D5" s="275">
         <f>'CO_Attainment for Unit Tests'!C4</f>
         <v>22414</v>
       </c>
-      <c r="E5" s="217"/>
+      <c r="E5" s="220"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
       <c r="H5" s="30"/>
@@ -14293,11 +14301,11 @@
       <c r="C6" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="263" t="str">
+      <c r="D6" s="275" t="str">
         <f>'CO_Attainment for Unit Tests'!C5</f>
         <v>4th SEM(CO4I SCHEME)</v>
       </c>
-      <c r="E6" s="217"/>
+      <c r="E6" s="220"/>
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
@@ -14321,11 +14329,11 @@
       <c r="C7" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="263" t="str">
+      <c r="D7" s="275" t="str">
         <f>'CO_Attainment for Unit Tests'!C6</f>
         <v>2023-24</v>
       </c>
-      <c r="E7" s="217"/>
+      <c r="E7" s="220"/>
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
       <c r="H7" s="30"/>
@@ -14348,43 +14356,43 @@
       <c r="E8" s="13"/>
     </row>
     <row r="9" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="264" t="s">
+      <c r="B9" s="283" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="265" t="s">
+      <c r="C9" s="278" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="227" t="s">
+      <c r="D9" s="269" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="265" t="s">
+      <c r="E9" s="278" t="s">
         <v>142</v>
       </c>
       <c r="J9" s="71"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
+      <c r="B10" s="254"/>
+      <c r="C10" s="254"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
       <c r="J10" s="72"/>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B11" s="223"/>
-      <c r="C11" s="223"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="223"/>
+      <c r="B11" s="254"/>
+      <c r="C11" s="254"/>
+      <c r="D11" s="254"/>
+      <c r="E11" s="254"/>
     </row>
     <row r="12" spans="2:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="223"/>
-      <c r="C12" s="223"/>
-      <c r="D12" s="223"/>
-      <c r="E12" s="224"/>
+      <c r="B12" s="254"/>
+      <c r="C12" s="254"/>
+      <c r="D12" s="254"/>
+      <c r="E12" s="255"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B13" s="224"/>
-      <c r="C13" s="224"/>
-      <c r="D13" s="224"/>
+      <c r="B13" s="255"/>
+      <c r="C13" s="255"/>
+      <c r="D13" s="255"/>
       <c r="E13" s="35">
         <v>70</v>
       </c>
@@ -15743,7 +15751,7 @@
       <c r="D97" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="E97" s="272">
+      <c r="E97" s="279">
         <f>D98*E13/100</f>
         <v>26.774999999999999</v>
       </c>
@@ -15752,7 +15760,7 @@
       <c r="D98" s="77">
         <v>38.25</v>
       </c>
-      <c r="E98" s="220"/>
+      <c r="E98" s="217"/>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="78" t="s">
@@ -15778,12 +15786,12 @@
       <c r="E102" s="13"/>
     </row>
     <row r="103" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="235" t="s">
+      <c r="A103" s="242" t="s">
         <v>130</v>
       </c>
-      <c r="B103" s="207"/>
-      <c r="C103" s="207"/>
-      <c r="D103" s="208"/>
+      <c r="B103" s="224"/>
+      <c r="C103" s="224"/>
+      <c r="D103" s="225"/>
       <c r="E103" s="82" t="s">
         <v>131</v>
       </c>
@@ -15795,17 +15803,17 @@
       <c r="I103" s="84"/>
     </row>
     <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="238" t="s">
+      <c r="A104" s="245" t="s">
         <v>133</v>
       </c>
       <c r="B104" s="85">
         <v>0.5</v>
       </c>
-      <c r="C104" s="273" t="s">
+      <c r="C104" s="280" t="s">
         <v>145</v>
       </c>
-      <c r="D104" s="274"/>
-      <c r="E104" s="275">
+      <c r="D104" s="281"/>
+      <c r="E104" s="282">
         <f>COUNTA(D14:D96)-COUNTIFS(D14:D96,0)</f>
         <v>62</v>
       </c>
@@ -15820,15 +15828,15 @@
       <c r="I104" s="84"/>
     </row>
     <row r="105" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="239"/>
+      <c r="A105" s="246"/>
       <c r="B105" s="88">
         <v>0.6</v>
       </c>
-      <c r="C105" s="266" t="s">
+      <c r="C105" s="284" t="s">
         <v>145</v>
       </c>
-      <c r="D105" s="261"/>
-      <c r="E105" s="219"/>
+      <c r="D105" s="252"/>
+      <c r="E105" s="216"/>
       <c r="F105" s="89">
         <f t="shared" si="0"/>
         <v>37.199999999999996</v>
@@ -15840,15 +15848,15 @@
       <c r="I105" s="84"/>
     </row>
     <row r="106" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="240"/>
+      <c r="A106" s="247"/>
       <c r="B106" s="91">
         <v>0.7</v>
       </c>
-      <c r="C106" s="267" t="s">
+      <c r="C106" s="285" t="s">
         <v>146</v>
       </c>
-      <c r="D106" s="233"/>
-      <c r="E106" s="220"/>
+      <c r="D106" s="240"/>
+      <c r="E106" s="217"/>
       <c r="F106" s="92">
         <f t="shared" si="0"/>
         <v>43.4</v>
@@ -15882,10 +15890,10 @@
       <c r="I108" s="84"/>
     </row>
     <row r="109" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="268" t="s">
+      <c r="A109" s="286" t="s">
         <v>147</v>
       </c>
-      <c r="B109" s="269"/>
+      <c r="B109" s="287"/>
       <c r="C109" s="66" t="s">
         <v>9</v>
       </c>
@@ -15907,10 +15915,10 @@
       <c r="I109" s="84"/>
     </row>
     <row r="110" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="270" t="s">
+      <c r="A110" s="276" t="s">
         <v>148</v>
       </c>
-      <c r="B110" s="271"/>
+      <c r="B110" s="277"/>
       <c r="C110" s="69">
         <f>IF(E99&gt;=$F106,3,IF(E99&gt;=$F105,2,IF(E99&gt;=$F104,1,0)))</f>
         <v>3</v>
@@ -17323,11 +17331,11 @@
       <c r="C4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="247" t="str">
+      <c r="D4" s="258" t="str">
         <f>'CO_Attainment for Unit Tests'!C3</f>
         <v xml:space="preserve"> Data Communication and Computer Network</v>
       </c>
-      <c r="E4" s="248"/>
+      <c r="E4" s="259"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
       <c r="H4" s="30"/>
@@ -17337,11 +17345,11 @@
       <c r="C5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="247">
+      <c r="D5" s="258">
         <f>'CO_Attainment for Unit Tests'!C4</f>
         <v>22414</v>
       </c>
-      <c r="E5" s="248"/>
+      <c r="E5" s="259"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
       <c r="H5" s="30"/>
@@ -17351,11 +17359,11 @@
       <c r="C6" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="247" t="str">
+      <c r="D6" s="258" t="str">
         <f>'CO_Attainment for Unit Tests'!C5</f>
         <v>4th SEM(CO4I SCHEME)</v>
       </c>
-      <c r="E6" s="248"/>
+      <c r="E6" s="259"/>
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
@@ -17365,63 +17373,63 @@
       <c r="C7" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="247" t="str">
+      <c r="D7" s="258" t="str">
         <f>'CO_Attainment for Unit Tests'!C6</f>
         <v>2023-24</v>
       </c>
-      <c r="E7" s="248"/>
+      <c r="E7" s="259"/>
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
       <c r="H7" s="30"/>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="264" t="s">
+      <c r="B9" s="283" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="265" t="s">
+      <c r="C9" s="278" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="276" t="s">
+      <c r="D9" s="288" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="282" t="s">
+      <c r="E9" s="290" t="s">
         <v>153</v>
       </c>
-      <c r="F9" s="283" t="s">
+      <c r="F9" s="291" t="s">
         <v>154</v>
       </c>
-      <c r="G9" s="283" t="s">
+      <c r="G9" s="291" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
+      <c r="B10" s="254"/>
+      <c r="C10" s="254"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="254"/>
+      <c r="G10" s="254"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="223"/>
-      <c r="C11" s="223"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="223"/>
-      <c r="F11" s="223"/>
-      <c r="G11" s="223"/>
+      <c r="B11" s="254"/>
+      <c r="C11" s="254"/>
+      <c r="D11" s="254"/>
+      <c r="E11" s="254"/>
+      <c r="F11" s="254"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="223"/>
-      <c r="C12" s="223"/>
-      <c r="D12" s="223"/>
-      <c r="E12" s="224"/>
-      <c r="F12" s="224"/>
-      <c r="G12" s="224"/>
+      <c r="B12" s="254"/>
+      <c r="C12" s="254"/>
+      <c r="D12" s="254"/>
+      <c r="E12" s="255"/>
+      <c r="F12" s="255"/>
+      <c r="G12" s="255"/>
     </row>
     <row r="13" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="224"/>
-      <c r="C13" s="224"/>
-      <c r="D13" s="224"/>
+      <c r="B13" s="255"/>
+      <c r="C13" s="255"/>
+      <c r="D13" s="255"/>
       <c r="E13" s="35">
         <v>10</v>
       </c>
@@ -19012,15 +19020,15 @@
       <c r="D97" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="E97" s="277">
+      <c r="E97" s="292">
         <f>ROUNDUP(D98*E13/100,1)</f>
         <v>6</v>
       </c>
-      <c r="F97" s="277">
+      <c r="F97" s="292">
         <f>ROUNDUP(D98*F13/100,1)</f>
         <v>15</v>
       </c>
-      <c r="G97" s="277">
+      <c r="G97" s="292">
         <f>ROUNDUP(D98*G13/100,1)</f>
         <v>15</v>
       </c>
@@ -19029,9 +19037,9 @@
       <c r="D98" s="98">
         <v>60</v>
       </c>
-      <c r="E98" s="220"/>
-      <c r="F98" s="220"/>
-      <c r="G98" s="220"/>
+      <c r="E98" s="217"/>
+      <c r="F98" s="217"/>
+      <c r="G98" s="217"/>
     </row>
     <row r="99" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="78" t="s">
@@ -19055,11 +19063,11 @@
     <row r="102" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="103" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="84"/>
-      <c r="B103" s="235" t="s">
+      <c r="B103" s="242" t="s">
         <v>157</v>
       </c>
-      <c r="C103" s="207"/>
-      <c r="D103" s="208"/>
+      <c r="C103" s="224"/>
+      <c r="D103" s="225"/>
       <c r="E103" s="99" t="s">
         <v>131</v>
       </c>
@@ -19071,7 +19079,7 @@
     </row>
     <row r="104" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="84"/>
-      <c r="B104" s="238" t="s">
+      <c r="B104" s="245" t="s">
         <v>133</v>
       </c>
       <c r="C104" s="85">
@@ -19080,7 +19088,7 @@
       <c r="D104" s="86" t="s">
         <v>146</v>
       </c>
-      <c r="E104" s="275">
+      <c r="E104" s="282">
         <f>COUNTA(D14:D96)-COUNTIFS(D14:D96,0)</f>
         <v>62</v>
       </c>
@@ -19095,14 +19103,14 @@
     </row>
     <row r="105" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="84"/>
-      <c r="B105" s="239"/>
+      <c r="B105" s="246"/>
       <c r="C105" s="88">
         <v>0.6</v>
       </c>
       <c r="D105" s="89" t="s">
         <v>146</v>
       </c>
-      <c r="E105" s="219"/>
+      <c r="E105" s="216"/>
       <c r="F105" s="101">
         <f>C105*$E104</f>
         <v>37.199999999999996</v>
@@ -19114,14 +19122,14 @@
     </row>
     <row r="106" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="84"/>
-      <c r="B106" s="240"/>
+      <c r="B106" s="247"/>
       <c r="C106" s="91">
         <v>0.7</v>
       </c>
       <c r="D106" s="92" t="s">
         <v>146</v>
       </c>
-      <c r="E106" s="220"/>
+      <c r="E106" s="217"/>
       <c r="F106" s="102">
         <f>C106*$E104</f>
         <v>43.4</v>
@@ -19152,10 +19160,10 @@
       <c r="H108" s="84"/>
     </row>
     <row r="109" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="221" t="s">
+      <c r="A109" s="223" t="s">
         <v>158</v>
       </c>
-      <c r="B109" s="278"/>
+      <c r="B109" s="293"/>
       <c r="C109" s="103" t="s">
         <v>9</v>
       </c>
@@ -19176,10 +19184,10 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="279" t="s">
+      <c r="A110" s="294" t="s">
         <v>159</v>
       </c>
-      <c r="B110" s="269"/>
+      <c r="B110" s="287"/>
       <c r="C110" s="105">
         <f>IF(E99&gt;=$F106,3,IF(E99&gt;=$F105,2,IF(E99&gt;=$F104,1,0)))</f>
         <v>3</v>
@@ -19206,10 +19214,10 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="280" t="s">
+      <c r="A111" s="295" t="s">
         <v>160</v>
       </c>
-      <c r="B111" s="248"/>
+      <c r="B111" s="259"/>
       <c r="C111" s="107">
         <f>IF(F99&gt;=$F106,3,IF(F99&gt;=$F105,2,IF(F99&gt;=$F104,1,0)))</f>
         <v>3</v>
@@ -19236,10 +19244,10 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="281" t="s">
+      <c r="A112" s="289" t="s">
         <v>161</v>
       </c>
-      <c r="B112" s="271"/>
+      <c r="B112" s="277"/>
       <c r="C112" s="69">
         <f>IF(G99&gt;=$F106,3,IF(G99&gt;=$F105,2,IF(G99&gt;=$F104,1,0)))</f>
         <v>3</v>
@@ -20286,41 +20294,41 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="290" t="s">
+      <c r="B10" s="298" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="291" t="s">
+      <c r="C10" s="299" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="292" t="s">
+      <c r="D10" s="300" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="291" t="s">
+      <c r="E10" s="299" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="219"/>
-      <c r="C11" s="219"/>
-      <c r="D11" s="219"/>
-      <c r="E11" s="219"/>
+      <c r="B11" s="216"/>
+      <c r="C11" s="216"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="216"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="219"/>
-      <c r="C12" s="219"/>
-      <c r="D12" s="219"/>
-      <c r="E12" s="219"/>
+      <c r="B12" s="216"/>
+      <c r="C12" s="216"/>
+      <c r="D12" s="216"/>
+      <c r="E12" s="216"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="219"/>
-      <c r="C13" s="219"/>
-      <c r="D13" s="219"/>
-      <c r="E13" s="293"/>
+      <c r="B13" s="216"/>
+      <c r="C13" s="216"/>
+      <c r="D13" s="216"/>
+      <c r="E13" s="301"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="220"/>
-      <c r="C14" s="220"/>
-      <c r="D14" s="220"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
       <c r="E14" s="112">
         <v>5</v>
       </c>
@@ -21117,57 +21125,57 @@
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="85" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="294" t="s">
+      <c r="A85" s="302" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="207"/>
-      <c r="C85" s="207"/>
-      <c r="D85" s="208"/>
+      <c r="B85" s="224"/>
+      <c r="C85" s="224"/>
+      <c r="D85" s="225"/>
       <c r="E85" s="119" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="295" t="s">
+      <c r="A86" s="303" t="s">
         <v>133</v>
       </c>
-      <c r="B86" s="296" t="s">
+      <c r="B86" s="304" t="s">
         <v>171</v>
       </c>
-      <c r="C86" s="297"/>
-      <c r="D86" s="274"/>
+      <c r="C86" s="305"/>
+      <c r="D86" s="281"/>
       <c r="E86" s="120">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="239"/>
-      <c r="B87" s="284" t="s">
+      <c r="A87" s="246"/>
+      <c r="B87" s="306" t="s">
         <v>172</v>
       </c>
-      <c r="C87" s="285"/>
-      <c r="D87" s="261"/>
+      <c r="C87" s="307"/>
+      <c r="D87" s="252"/>
       <c r="E87" s="121">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="240"/>
-      <c r="B88" s="286" t="s">
+      <c r="A88" s="247"/>
+      <c r="B88" s="308" t="s">
         <v>173</v>
       </c>
-      <c r="C88" s="287"/>
-      <c r="D88" s="233"/>
+      <c r="C88" s="309"/>
+      <c r="D88" s="240"/>
       <c r="E88" s="122">
         <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="90" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="288" t="s">
+      <c r="A90" s="296" t="s">
         <v>158</v>
       </c>
-      <c r="B90" s="278"/>
+      <c r="B90" s="293"/>
       <c r="C90" s="123" t="s">
         <v>9</v>
       </c>
@@ -21185,10 +21193,10 @@
       </c>
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="289" t="s">
+      <c r="A91" s="297" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="269"/>
+      <c r="B91" s="287"/>
       <c r="C91" s="125">
         <f>IF(E81&gt;=80,3,IF(E81&gt;=65,2,IF(E81&gt;=40,1,0)))</f>
         <v>0</v>
@@ -22205,34 +22213,34 @@
       <c r="P5" s="13"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="218" t="s">
+      <c r="B6" s="215" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="200" t="s">
+      <c r="C6" s="226" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="201"/>
-      <c r="E6" s="221" t="s">
+      <c r="D6" s="227"/>
+      <c r="E6" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="207"/>
-      <c r="G6" s="207"/>
-      <c r="H6" s="207"/>
-      <c r="I6" s="207"/>
-      <c r="J6" s="207"/>
-      <c r="K6" s="207"/>
-      <c r="L6" s="207"/>
-      <c r="M6" s="207"/>
-      <c r="N6" s="208"/>
-      <c r="O6" s="221" t="s">
+      <c r="F6" s="224"/>
+      <c r="G6" s="224"/>
+      <c r="H6" s="224"/>
+      <c r="I6" s="224"/>
+      <c r="J6" s="224"/>
+      <c r="K6" s="224"/>
+      <c r="L6" s="224"/>
+      <c r="M6" s="224"/>
+      <c r="N6" s="225"/>
+      <c r="O6" s="223" t="s">
         <v>24</v>
       </c>
-      <c r="P6" s="208"/>
+      <c r="P6" s="225"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="219"/>
-      <c r="C7" s="202"/>
-      <c r="D7" s="203"/>
+      <c r="B7" s="216"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="229"/>
       <c r="E7" s="15" t="s">
         <v>25</v>
       </c>
@@ -22271,9 +22279,9 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="62.25" x14ac:dyDescent="0.25">
-      <c r="B8" s="220"/>
-      <c r="C8" s="204"/>
-      <c r="D8" s="205"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="230"/>
+      <c r="D8" s="231"/>
       <c r="E8" s="16" t="s">
         <v>183</v>
       </c>
@@ -22594,11 +22602,11 @@
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="298" t="s">
+      <c r="B15" s="310" t="s">
         <v>202</v>
       </c>
-      <c r="C15" s="207"/>
-      <c r="D15" s="208"/>
+      <c r="C15" s="224"/>
+      <c r="D15" s="225"/>
       <c r="E15" s="132">
         <f t="shared" ref="E15:P15" si="0">ROUNDUP(AVERAGE(E9:E14),2)</f>
         <v>3</v>
@@ -22649,11 +22657,11 @@
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="299" t="s">
+      <c r="B16" s="311" t="s">
         <v>203</v>
       </c>
-      <c r="C16" s="207"/>
-      <c r="D16" s="208"/>
+      <c r="C16" s="224"/>
+      <c r="D16" s="225"/>
       <c r="E16" s="133">
         <f t="shared" ref="E16:P16" si="1">ROUNDUP((E15*2.66)/3,2)</f>
         <v>2.66</v>
@@ -22704,11 +22712,11 @@
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="299" t="s">
+      <c r="B17" s="311" t="s">
         <v>204</v>
       </c>
-      <c r="C17" s="207"/>
-      <c r="D17" s="208"/>
+      <c r="C17" s="224"/>
+      <c r="D17" s="225"/>
       <c r="E17" s="133">
         <f t="shared" ref="E17:P17" si="2">ROUNDUP((E16/3)*100,2)</f>
         <v>88.67</v>
@@ -23740,13 +23748,13 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:D8"/>
     <mergeCell ref="E6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -23995,16 +24003,16 @@
     <row r="8" spans="1:26" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
-      <c r="C8" s="300" t="s">
+      <c r="C8" s="312" t="s">
         <v>206</v>
       </c>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
-      <c r="H8" s="207"/>
-      <c r="I8" s="207"/>
-      <c r="J8" s="208"/>
+      <c r="D8" s="224"/>
+      <c r="E8" s="224"/>
+      <c r="F8" s="224"/>
+      <c r="G8" s="224"/>
+      <c r="H8" s="224"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="225"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
@@ -24025,18 +24033,18 @@
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
-      <c r="C9" s="301" t="s">
+      <c r="C9" s="313" t="s">
         <v>207</v>
       </c>
-      <c r="D9" s="207"/>
-      <c r="E9" s="207"/>
-      <c r="F9" s="207"/>
-      <c r="G9" s="207"/>
-      <c r="H9" s="208"/>
-      <c r="I9" s="302" t="s">
+      <c r="D9" s="224"/>
+      <c r="E9" s="224"/>
+      <c r="F9" s="224"/>
+      <c r="G9" s="224"/>
+      <c r="H9" s="225"/>
+      <c r="I9" s="314" t="s">
         <v>208</v>
       </c>
-      <c r="J9" s="201"/>
+      <c r="J9" s="227"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
@@ -24057,20 +24065,20 @@
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
-      <c r="C10" s="303" t="s">
+      <c r="C10" s="315" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="304" t="s">
+      <c r="D10" s="316" t="s">
         <v>210</v>
       </c>
-      <c r="E10" s="305"/>
-      <c r="F10" s="305"/>
-      <c r="G10" s="205"/>
+      <c r="E10" s="317"/>
+      <c r="F10" s="317"/>
+      <c r="G10" s="231"/>
       <c r="H10" s="135" t="s">
         <v>211</v>
       </c>
-      <c r="I10" s="204"/>
-      <c r="J10" s="205"/>
+      <c r="I10" s="230"/>
+      <c r="J10" s="231"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
@@ -24091,7 +24099,7 @@
     <row r="11" spans="1:26" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
-      <c r="C11" s="220"/>
+      <c r="C11" s="217"/>
       <c r="D11" s="136" t="s">
         <v>212</v>
       </c>
@@ -24107,10 +24115,10 @@
       <c r="H11" s="139" t="s">
         <v>215</v>
       </c>
-      <c r="I11" s="306" t="s">
+      <c r="I11" s="318" t="s">
         <v>216</v>
       </c>
-      <c r="J11" s="208"/>
+      <c r="J11" s="225"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="13"/>
@@ -24154,11 +24162,11 @@
         <f>'CO_attainment for FA-TH ESE'!C110</f>
         <v>3</v>
       </c>
-      <c r="I12" s="307">
+      <c r="I12" s="319">
         <f>'CO_attainment for Indirect'!C91</f>
         <v>0</v>
       </c>
-      <c r="J12" s="274"/>
+      <c r="J12" s="281"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
@@ -24202,11 +24210,11 @@
         <f t="shared" ref="H13:H17" si="3">$H12</f>
         <v>3</v>
       </c>
-      <c r="I13" s="311">
+      <c r="I13" s="323">
         <f t="shared" ref="I13:I17" si="4">$I12</f>
         <v>0</v>
       </c>
-      <c r="J13" s="261"/>
+      <c r="J13" s="252"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
@@ -24250,11 +24258,11 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I14" s="311">
+      <c r="I14" s="323">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J14" s="261"/>
+      <c r="J14" s="252"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
@@ -24298,11 +24306,11 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I15" s="311">
+      <c r="I15" s="323">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J15" s="261"/>
+      <c r="J15" s="252"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
@@ -24346,11 +24354,11 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I16" s="311">
+      <c r="I16" s="323">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J16" s="261"/>
+      <c r="J16" s="252"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
@@ -24394,11 +24402,11 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I17" s="311">
+      <c r="I17" s="323">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J17" s="261"/>
+      <c r="J17" s="252"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
@@ -24442,11 +24450,11 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I18" s="307">
+      <c r="I18" s="319">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J18" s="274"/>
+      <c r="J18" s="281"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
@@ -24485,10 +24493,10 @@
       <c r="H19" s="153">
         <v>60</v>
       </c>
-      <c r="I19" s="312">
+      <c r="I19" s="324">
         <v>100</v>
       </c>
-      <c r="J19" s="248"/>
+      <c r="J19" s="259"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
@@ -24532,11 +24540,11 @@
         <f t="shared" si="6"/>
         <v>1.8</v>
       </c>
-      <c r="I20" s="308">
+      <c r="I20" s="320">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J20" s="233"/>
+      <c r="J20" s="240"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
@@ -24557,13 +24565,13 @@
     <row r="21" spans="1:26" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
-      <c r="C21" s="309" t="s">
+      <c r="C21" s="321" t="s">
         <v>220</v>
       </c>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
-      <c r="F21" s="207"/>
-      <c r="G21" s="208"/>
+      <c r="D21" s="224"/>
+      <c r="E21" s="224"/>
+      <c r="F21" s="224"/>
+      <c r="G21" s="225"/>
       <c r="H21" s="155">
         <f>SUM(D20:H20)</f>
         <v>2.867</v>
@@ -24595,13 +24603,13 @@
     <row r="22" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
-      <c r="C22" s="309" t="s">
+      <c r="C22" s="321" t="s">
         <v>222</v>
       </c>
-      <c r="D22" s="207"/>
-      <c r="E22" s="207"/>
-      <c r="F22" s="207"/>
-      <c r="G22" s="208"/>
+      <c r="D22" s="224"/>
+      <c r="E22" s="224"/>
+      <c r="F22" s="224"/>
+      <c r="G22" s="225"/>
       <c r="H22" s="157">
         <v>0.8</v>
       </c>
@@ -24631,13 +24639,13 @@
     <row r="23" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
-      <c r="C23" s="309" t="s">
+      <c r="C23" s="321" t="s">
         <v>224</v>
       </c>
-      <c r="D23" s="207"/>
-      <c r="E23" s="207"/>
-      <c r="F23" s="207"/>
-      <c r="G23" s="208"/>
+      <c r="D23" s="224"/>
+      <c r="E23" s="224"/>
+      <c r="F23" s="224"/>
+      <c r="G23" s="225"/>
       <c r="H23" s="155">
         <f>0.8*H21</f>
         <v>2.2936000000000001</v>
@@ -24669,14 +24677,14 @@
     <row r="24" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
-      <c r="C24" s="310" t="s">
+      <c r="C24" s="322" t="s">
         <v>226</v>
       </c>
-      <c r="D24" s="207"/>
-      <c r="E24" s="207"/>
-      <c r="F24" s="207"/>
-      <c r="G24" s="207"/>
-      <c r="H24" s="208"/>
+      <c r="D24" s="224"/>
+      <c r="E24" s="224"/>
+      <c r="F24" s="224"/>
+      <c r="G24" s="224"/>
+      <c r="H24" s="225"/>
       <c r="I24" s="159">
         <f>ROUNDUP(H23+J23,2)</f>
         <v>2.2999999999999998</v>
@@ -31538,15 +31546,15 @@
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="30"/>
-      <c r="C8" s="313" t="s">
+      <c r="C8" s="325" t="s">
         <v>229</v>
       </c>
-      <c r="D8" s="314"/>
-      <c r="E8" s="316" t="s">
+      <c r="D8" s="326"/>
+      <c r="E8" s="328" t="s">
         <v>230</v>
       </c>
-      <c r="F8" s="297"/>
-      <c r="G8" s="269"/>
+      <c r="F8" s="305"/>
+      <c r="G8" s="287"/>
       <c r="H8" s="161" t="s">
         <v>154</v>
       </c>
@@ -31556,7 +31564,7 @@
       <c r="J8" s="161" t="s">
         <v>231</v>
       </c>
-      <c r="K8" s="317" t="s">
+      <c r="K8" s="329" t="s">
         <v>232</v>
       </c>
       <c r="L8" s="13"/>
@@ -31578,8 +31586,8 @@
     <row r="9" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="30"/>
-      <c r="C9" s="204"/>
-      <c r="D9" s="315"/>
+      <c r="C9" s="230"/>
+      <c r="D9" s="327"/>
       <c r="E9" s="162" t="s">
         <v>233</v>
       </c>
@@ -31598,7 +31606,7 @@
       <c r="J9" s="163" t="s">
         <v>215</v>
       </c>
-      <c r="K9" s="318"/>
+      <c r="K9" s="330"/>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
@@ -31618,14 +31626,14 @@
     <row r="10" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="30"/>
-      <c r="C10" s="319" t="s">
+      <c r="C10" s="331" t="s">
         <v>237</v>
       </c>
-      <c r="D10" s="269"/>
-      <c r="E10" s="320">
+      <c r="D10" s="287"/>
+      <c r="E10" s="332">
         <v>20</v>
       </c>
-      <c r="F10" s="269"/>
+      <c r="F10" s="287"/>
       <c r="G10" s="164">
         <v>10</v>
       </c>
@@ -31661,15 +31669,15 @@
     <row r="11" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="30"/>
-      <c r="C11" s="321" t="s">
+      <c r="C11" s="333" t="s">
         <v>238</v>
       </c>
-      <c r="D11" s="271"/>
-      <c r="E11" s="322">
+      <c r="D11" s="277"/>
+      <c r="E11" s="334">
         <f>(E10/$K10)*100</f>
         <v>13.333333333333334</v>
       </c>
-      <c r="F11" s="271"/>
+      <c r="F11" s="277"/>
       <c r="G11" s="165">
         <f t="shared" ref="G11:J11" si="1">(G10/$K10)*100</f>
         <v>6.666666666666667</v>
@@ -31793,16 +31801,16 @@
     <row r="15" spans="1:26" ht="21" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
-      <c r="C15" s="323" t="s">
+      <c r="C15" s="335" t="s">
         <v>206</v>
       </c>
-      <c r="D15" s="207"/>
-      <c r="E15" s="207"/>
-      <c r="F15" s="207"/>
-      <c r="G15" s="207"/>
-      <c r="H15" s="207"/>
-      <c r="I15" s="207"/>
-      <c r="J15" s="208"/>
+      <c r="D15" s="224"/>
+      <c r="E15" s="224"/>
+      <c r="F15" s="224"/>
+      <c r="G15" s="224"/>
+      <c r="H15" s="224"/>
+      <c r="I15" s="224"/>
+      <c r="J15" s="225"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
@@ -31823,16 +31831,16 @@
     <row r="16" spans="1:26" ht="21" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
-      <c r="C16" s="324" t="s">
+      <c r="C16" s="336" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="207"/>
-      <c r="G16" s="207"/>
-      <c r="H16" s="208"/>
-      <c r="I16" s="325"/>
-      <c r="J16" s="201"/>
+      <c r="D16" s="224"/>
+      <c r="E16" s="224"/>
+      <c r="F16" s="224"/>
+      <c r="G16" s="224"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="337"/>
+      <c r="J16" s="227"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
@@ -31853,7 +31861,7 @@
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
-      <c r="C17" s="326" t="s">
+      <c r="C17" s="338" t="s">
         <v>239</v>
       </c>
       <c r="D17" s="167"/>
@@ -31865,8 +31873,8 @@
       <c r="H17" s="171" t="s">
         <v>211</v>
       </c>
-      <c r="I17" s="204"/>
-      <c r="J17" s="205"/>
+      <c r="I17" s="230"/>
+      <c r="J17" s="231"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
@@ -31887,7 +31895,7 @@
     <row r="18" spans="1:26" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
-      <c r="C18" s="220"/>
+      <c r="C18" s="217"/>
       <c r="D18" s="172" t="s">
         <v>212</v>
       </c>
@@ -31903,8 +31911,8 @@
       <c r="H18" s="175" t="s">
         <v>215</v>
       </c>
-      <c r="I18" s="327"/>
-      <c r="J18" s="208"/>
+      <c r="I18" s="339"/>
+      <c r="J18" s="225"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
@@ -31948,8 +31956,8 @@
         <f>'CO_attainment for FA-TH ESE'!C110</f>
         <v>3</v>
       </c>
-      <c r="I19" s="328"/>
-      <c r="J19" s="274"/>
+      <c r="I19" s="340"/>
+      <c r="J19" s="281"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
@@ -31993,8 +32001,8 @@
         <f t="shared" ref="H20:H24" si="5">$H19</f>
         <v>3</v>
       </c>
-      <c r="I20" s="329"/>
-      <c r="J20" s="261"/>
+      <c r="I20" s="341"/>
+      <c r="J20" s="252"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
@@ -32019,7 +32027,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="180">
-        <f>'CO_Attainment for Unit Tests'!F109</f>
+        <f>'CO_Attainment for Unit Tests'!E110</f>
         <v>0</v>
       </c>
       <c r="E21" s="181">
@@ -32038,8 +32046,8 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I21" s="329"/>
-      <c r="J21" s="261"/>
+      <c r="I21" s="341"/>
+      <c r="J21" s="252"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
@@ -32083,8 +32091,8 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I22" s="329"/>
-      <c r="J22" s="261"/>
+      <c r="I22" s="341"/>
+      <c r="J22" s="252"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
@@ -32128,8 +32136,8 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I23" s="329"/>
-      <c r="J23" s="261"/>
+      <c r="I23" s="341"/>
+      <c r="J23" s="252"/>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
@@ -32173,8 +32181,8 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I24" s="329"/>
-      <c r="J24" s="261"/>
+      <c r="I24" s="341"/>
+      <c r="J24" s="252"/>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
@@ -32192,7 +32200,7 @@
       <c r="Y24" s="13"/>
       <c r="Z24" s="13"/>
     </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="176" t="s">
@@ -32218,8 +32226,8 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="I25" s="328"/>
-      <c r="J25" s="274"/>
+      <c r="I25" s="340"/>
+      <c r="J25" s="281"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
@@ -32237,7 +32245,7 @@
       <c r="Y25" s="13"/>
       <c r="Z25" s="13"/>
     </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="186" t="s">
@@ -32263,8 +32271,8 @@
         <f t="shared" si="7"/>
         <v>46.666666666666664</v>
       </c>
-      <c r="I26" s="333"/>
-      <c r="J26" s="261"/>
+      <c r="I26" s="345"/>
+      <c r="J26" s="252"/>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
       <c r="M26" s="13"/>
@@ -32282,7 +32290,7 @@
       <c r="Y26" s="13"/>
       <c r="Z26" s="13"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="188" t="s">
@@ -32308,8 +32316,8 @@
         <f t="shared" si="8"/>
         <v>1.4</v>
       </c>
-      <c r="I27" s="334"/>
-      <c r="J27" s="233"/>
+      <c r="I27" s="346"/>
+      <c r="J27" s="240"/>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
       <c r="M27" s="13"/>
@@ -32327,16 +32335,16 @@
       <c r="Y27" s="13"/>
       <c r="Z27" s="13"/>
     </row>
-    <row r="28" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
-      <c r="C28" s="330" t="s">
+      <c r="C28" s="342" t="s">
         <v>220</v>
       </c>
-      <c r="D28" s="207"/>
-      <c r="E28" s="207"/>
-      <c r="F28" s="207"/>
-      <c r="G28" s="208"/>
+      <c r="D28" s="224"/>
+      <c r="E28" s="224"/>
+      <c r="F28" s="224"/>
+      <c r="G28" s="225"/>
       <c r="H28" s="190">
         <f>SUM(D27:H27)</f>
         <v>2.8226666666666667</v>
@@ -32360,16 +32368,16 @@
       <c r="Y28" s="13"/>
       <c r="Z28" s="13"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
-      <c r="C29" s="330" t="s">
+      <c r="C29" s="342" t="s">
         <v>222</v>
       </c>
-      <c r="D29" s="207"/>
-      <c r="E29" s="207"/>
-      <c r="F29" s="207"/>
-      <c r="G29" s="208"/>
+      <c r="D29" s="224"/>
+      <c r="E29" s="224"/>
+      <c r="F29" s="224"/>
+      <c r="G29" s="225"/>
       <c r="H29" s="193">
         <v>1</v>
       </c>
@@ -32395,13 +32403,13 @@
     <row r="30" spans="1:26" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
-      <c r="C30" s="330" t="s">
+      <c r="C30" s="342" t="s">
         <v>224</v>
       </c>
-      <c r="D30" s="207"/>
-      <c r="E30" s="207"/>
-      <c r="F30" s="207"/>
-      <c r="G30" s="208"/>
+      <c r="D30" s="224"/>
+      <c r="E30" s="224"/>
+      <c r="F30" s="224"/>
+      <c r="G30" s="225"/>
       <c r="H30" s="190">
         <f>H29*H28</f>
         <v>2.8226666666666667</v>
@@ -32428,14 +32436,14 @@
     <row r="31" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
-      <c r="C31" s="331" t="s">
+      <c r="C31" s="343" t="s">
         <v>226</v>
       </c>
-      <c r="D31" s="207"/>
-      <c r="E31" s="207"/>
-      <c r="F31" s="207"/>
-      <c r="G31" s="207"/>
-      <c r="H31" s="208"/>
+      <c r="D31" s="224"/>
+      <c r="E31" s="224"/>
+      <c r="F31" s="224"/>
+      <c r="G31" s="224"/>
+      <c r="H31" s="225"/>
       <c r="I31" s="195">
         <f>H30+J30</f>
         <v>2.8226666666666667</v>
@@ -32522,7 +32530,7 @@
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
-      <c r="H34" s="215" t="s">
+      <c r="H34" s="218" t="s">
         <v>46</v>
       </c>
       <c r="I34" s="213"/>
@@ -32551,11 +32559,11 @@
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
-      <c r="H35" s="332" t="s">
+      <c r="H35" s="344" t="s">
         <v>47</v>
       </c>
-      <c r="I35" s="217"/>
-      <c r="J35" s="217"/>
+      <c r="I35" s="220"/>
+      <c r="J35" s="220"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
@@ -39031,11 +39039,11 @@
       <c r="C2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="247" t="str">
+      <c r="D2" s="258" t="str">
         <f>'Overall CO attainment'!D3</f>
         <v xml:space="preserve"> Data Communication and Computer Network</v>
       </c>
-      <c r="E2" s="248"/>
+      <c r="E2" s="259"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -39063,11 +39071,11 @@
       <c r="C3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="247">
+      <c r="D3" s="258">
         <f>'Overall CO attainment'!D4</f>
         <v>22414</v>
       </c>
-      <c r="E3" s="248"/>
+      <c r="E3" s="259"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -39095,11 +39103,11 @@
       <c r="C4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="247" t="str">
+      <c r="D4" s="258" t="str">
         <f>'Overall CO attainment'!D5</f>
         <v>4th SEM(CO4I SCHEME)</v>
       </c>
-      <c r="E4" s="248"/>
+      <c r="E4" s="259"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -39127,11 +39135,11 @@
       <c r="C5" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="D5" s="247" t="str">
+      <c r="D5" s="258" t="str">
         <f>'Overall CO attainment'!D6</f>
         <v>2023-24</v>
       </c>
-      <c r="E5" s="248"/>
+      <c r="E5" s="259"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -39236,28 +39244,28 @@
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="218" t="s">
+      <c r="B9" s="215" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="200" t="s">
+      <c r="C9" s="226" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="201"/>
-      <c r="E9" s="221" t="s">
+      <c r="D9" s="227"/>
+      <c r="E9" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="207"/>
-      <c r="G9" s="207"/>
-      <c r="H9" s="207"/>
-      <c r="I9" s="207"/>
-      <c r="J9" s="207"/>
-      <c r="K9" s="208"/>
-      <c r="L9" s="221" t="s">
+      <c r="F9" s="224"/>
+      <c r="G9" s="224"/>
+      <c r="H9" s="224"/>
+      <c r="I9" s="224"/>
+      <c r="J9" s="224"/>
+      <c r="K9" s="225"/>
+      <c r="L9" s="223" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="208"/>
+      <c r="M9" s="225"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -39271,11 +39279,11 @@
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
     </row>
-    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="219"/>
-      <c r="C10" s="202"/>
-      <c r="D10" s="203"/>
+      <c r="B10" s="216"/>
+      <c r="C10" s="228"/>
+      <c r="D10" s="229"/>
       <c r="E10" s="15" t="s">
         <v>25</v>
       </c>
@@ -39318,9 +39326,9 @@
     </row>
     <row r="11" spans="1:25" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="220"/>
-      <c r="C11" s="204"/>
-      <c r="D11" s="205"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="230"/>
+      <c r="D11" s="231"/>
       <c r="E11" s="16" t="s">
         <v>34</v>
       </c>
@@ -39627,7 +39635,10 @@
         <f>'PO Set Target attain level'!D24</f>
         <v>Configure different TCP/IP services.</v>
       </c>
-      <c r="E16" s="197"/>
+      <c r="E16" s="197">
+        <f>'PO Set Target attain level'!E24</f>
+        <v>2</v>
+      </c>
       <c r="F16" s="197">
         <f>'PO Set Target attain level'!F24</f>
         <v>1</v>
@@ -39675,14 +39686,14 @@
     </row>
     <row r="17" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="206" t="s">
+      <c r="B17" s="232" t="s">
         <v>242</v>
       </c>
-      <c r="C17" s="207"/>
-      <c r="D17" s="208"/>
+      <c r="C17" s="224"/>
+      <c r="D17" s="225"/>
       <c r="E17" s="18">
         <f t="shared" ref="E17:M17" si="0">IFERROR(AVERAGE(E12:E16),0)</f>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F17" s="18">
         <f t="shared" si="0"/>
@@ -39731,14 +39742,14 @@
     </row>
     <row r="18" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="209" t="s">
+      <c r="B18" s="233" t="s">
         <v>243</v>
       </c>
-      <c r="C18" s="207"/>
-      <c r="D18" s="208"/>
+      <c r="C18" s="224"/>
+      <c r="D18" s="225"/>
       <c r="E18" s="198">
         <f>E17*'Overall CO attainment'!I31/3</f>
-        <v>2.3522222222222222</v>
+        <v>2.2581333333333333</v>
       </c>
       <c r="F18" s="198">
         <f>F17*'Overall CO attainment'!I31/3</f>
@@ -39787,14 +39798,14 @@
     </row>
     <row r="19" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="299" t="s">
+      <c r="B19" s="311" t="s">
         <v>204</v>
       </c>
-      <c r="C19" s="207"/>
-      <c r="D19" s="208"/>
+      <c r="C19" s="224"/>
+      <c r="D19" s="225"/>
       <c r="E19" s="133">
         <f t="shared" ref="E19:M19" si="1">ROUNDUP((E18/3)*100,2)</f>
-        <v>78.410000000000011</v>
+        <v>75.28</v>
       </c>
       <c r="F19" s="133">
         <f t="shared" si="1"/>
@@ -39905,7 +39916,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="215" t="s">
+      <c r="J22" s="218" t="s">
         <v>46</v>
       </c>
       <c r="K22" s="213"/>
@@ -39934,12 +39945,12 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="216" t="s">
+      <c r="J23" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="K23" s="217"/>
-      <c r="L23" s="217"/>
-      <c r="M23" s="217"/>
+      <c r="K23" s="220"/>
+      <c r="L23" s="220"/>
+      <c r="M23" s="220"/>
       <c r="N23" s="29"/>
       <c r="O23" s="29"/>
       <c r="P23" s="4"/>
